--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1115,10 +1115,8 @@
           <t>Ravi Shahi</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851071622</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851071622</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1208,25 +1206,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.30718</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.30718</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1327,10 +1321,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1420,25 +1412,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -572,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,14 +664,14 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -651,7 +687,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -666,12 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,6 +748,16 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -700,34 +771,71 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>1</v>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -741,11 +849,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -754,40 +862,40 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1460,6 +1568,642 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364446</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Jeet Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Jeet Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9823773885</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9840938326</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:30:31 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.701075</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Pepsicola,forcepark buspark	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L56-4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.379044</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 10m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364411</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bijya Lama</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bijya Lama</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9843955238</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9843955238</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:06:35 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.68945</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>pepsicola Punchmukhi chowk . ward -35,kageshwori  municipality kathmandu Baghmati Nepal , Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>bj.lama987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>08:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.36467</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>sbt connection</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363024</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9803357149</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46:50 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803357149</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:22:13 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46:50 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ktm tokha chowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>regmi8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L14-8</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 24m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1635,10 +1635,8 @@
           <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9823773885</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9823773885</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1728,25 +1726,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L56-4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.379044</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.37904399999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1847,10 +1841,8 @@
           <t>Bijya Lama</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9843955238</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9843955238</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1944,25 +1936,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.36467</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.36467</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2063,10 +2051,8 @@
           <t>Sundar Regmi</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9803357149</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9803357149</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2138,10 +2124,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="inlineStr"/>
       <c r="AJ6" s="3" t="inlineStr"/>
@@ -2156,10 +2140,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2170,35 +2152,239 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 24m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>02:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2d 24m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,72 +528,90 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chandramani Tharu</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -698,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -725,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,20 +762,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -772,13 +796,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>4</v>
+      <c r="F2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -794,9 +821,12 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -807,15 +837,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -826,16 +859,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -879,11 +915,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2253,10 +2289,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2342,10 +2376,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2356,37 +2388,897 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>03:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>03:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364756</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>New Assist Traders</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>New Assist Traders</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841756485</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841756485</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:35 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68162</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Big Mart Warehouse, Sankhamul - Balkumari Rd 11, Lalitpur - Near Big Mart Warehouse, Sankhamul</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>bhattaraidipesh96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>04:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32741</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>6d 1h 58m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358080</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:29:39 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.65564</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>27.65564, 85.3402, New Ganesh Temple Naya Basti, M84Q+9V5, Mahalaxmi 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3402</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 43m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -925,7 +925,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2489,10 +2489,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2586,25 +2584,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2705,10 +2699,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2802,25 +2794,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2911,20 +2899,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>New Assist Traders</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841756485</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841756485</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -3018,25 +3000,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,16</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32741</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32741</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3137,10 +3115,8 @@
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841479122</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841479122</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3230,55 +3206,263 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3402</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.3402</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 43m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.67713</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near by radhe radhe Vatbhatini, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>21:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L64-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.395276</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>5d 20h 43m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>4d 19h 49m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX11" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -802,10 +802,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -868,10 +868,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3311,20 +3311,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Puspa KC</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3414,55 +3408,695 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L64-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.395276</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.395276</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>4d 19h 49m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365031</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Prem Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Prem Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9840755152</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9840755152</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:56:52 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.7483</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Baniyatar Road,Jalpa Chowk, Opposite Himalayan Valley English Boarding School, Kathmandu, Bagmati, C</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L39-1</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.31749</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>4d 19h 49m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>13h 44m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9803334769</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9861500589</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.69044</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Naya Basti, Kuleshwor Height Pani Tanki, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>chiraniyagyan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>02:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB297</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.29494</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9803334769</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9861500589</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.69044</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Naya Basti, Kuleshwor Height Pani Tanki, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>chiraniyagyan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>02:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB297</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.29494</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -833,14 +833,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -853,25 +853,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>12</v>
+      <c r="F6" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3523,10 +3545,8 @@
           <t>Prem Kumar Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9840755152</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9840755152</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3616,25 +3636,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L39-1</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.31749</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.31749000000001</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3735,10 +3751,8 @@
           <t>Gyan Chiraniya</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9803334769</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9803334769</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3832,25 +3846,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB297</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.29494</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.29494</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3951,10 +3961,8 @@
           <t>Gyan Chiraniya</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9803334769</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9803334769</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4048,53 +4056,473 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB297</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.29494</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.29494</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>2d 20h 52m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>2d 20h 52m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362055</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.68556</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Sanepa Meat Shop Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>kapilshahi885@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>03:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.30718</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 11m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364261</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9826039231</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9826039231</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:23:09 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Dallu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>triratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>11:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -802,16 +802,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -833,11 +833,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -855,14 +855,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -875,25 +875,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>13</v>
+      <c r="D7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4171,10 +4193,8 @@
           <t>Ravi Shahi</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851071622</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851071622</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4268,25 +4288,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.30718</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.30718</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4387,10 +4403,8 @@
           <t>Niratna manandhar</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9826039231</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9826039231</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4480,10 +4494,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4494,37 +4506,453 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360378</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841390735</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841390735</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:38 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.751766</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Manmaiju chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>17:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.308081</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 37m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX17" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>low wifi range issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365280</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841121934</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841121934</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:00:04 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Nagar Bus Stop - Bus stop Araniko Highway Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>atul.mansur100@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>02:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L20-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -909,13 +909,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4593,20 +4593,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Maheshwor Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841390735</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841390735</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4696,25 +4690,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.308081</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.308081</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4815,10 +4805,8 @@
           <t>Atul Ali</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841121934</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841121934</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4908,10 +4896,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4922,35 +4908,243 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364910</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Duwal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Duwal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9869078453</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9869078453</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:57:31 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Surya Binayayak Near khopa engeneering college, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>duwalaayush234@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L3-4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>2h 6m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -802,10 +802,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -877,17 +877,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -897,25 +897,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>16</v>
+      <c r="D8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -942,12 +964,12 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -957,7 +979,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -5009,10 +5031,8 @@
           <t>Ayush Duwal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9869078453</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9869078453</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5102,10 +5122,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -5116,37 +5134,1101 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364848</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Mayanka Kirana Store</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Mayanka Kirana Store</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:45:00 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.666563</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near Preciois school,Bhaktapur Municipality, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>04:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L4-1</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.374291</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>17h 32m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>18h 50m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364245</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Banking Stack Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Banking Stack Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9801098007</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45:25 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9801098007</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:12:34 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45:25 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.740113</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near Trimurti Academy,Maharajgunj, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>buddha.thapa@mail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L21-3</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.346797</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Q856+RH2 Road Tarakeshwar 44600,Q856+RH2 Road Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>dangolsanjay292@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>04:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Q856+RH2 Road Tarakeshwar 44600,Q856+RH2 Road Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>dangolsanjay292@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>04:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362114</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9840860400</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9810388424</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:17:23 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.74363</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>punam02shah@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L57-4</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.3155</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -805,7 +805,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4</v>
@@ -937,7 +937,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5225,20 +5225,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Mayanka Kirana Store</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9844294603</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9844294603</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5314,10 +5308,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
@@ -5336,25 +5328,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L4-1</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.374291</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.374291</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5455,10 +5443,8 @@
           <t>Banking Stack Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9801098007</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9801098007</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5548,25 +5534,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L21-3</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.346797</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.346797</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5667,10 +5649,8 @@
           <t>Sanjay Dangol</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9840877910</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9840877910</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5760,10 +5740,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5774,7 +5752,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5875,10 +5853,8 @@
           <t>Sanjay Dangol</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9840877910</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9840877910</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5968,10 +5944,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5982,7 +5956,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6083,10 +6057,8 @@
           <t>Punam shah</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9840860400</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9840860400</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6180,47 +6152,43 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L57-4</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.3155</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.3155</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>2d 21h 16m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -6229,6 +6197,218 @@
       <c r="AX25" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:50 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364639</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pradhan</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pradhan</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851100323</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851100323</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:50:22 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.73338</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Ranibari -03, Nearby Takshashila Academy Higher Sec. School, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>07:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L10-8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.31954</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -802,10 +802,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -934,10 +934,10 @@
         <v>6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX26"/>
+  <dimension ref="A1:AX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6267,10 +6267,8 @@
           <t>Anil Pradhan</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851100323</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851100323</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6360,47 +6358,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L10-8</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.31954</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.31954</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>21h 44m</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>21h 44m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -6409,6 +6403,210 @@
       <c r="AX26" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364684</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:16:31 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Dhapasi Height Details from Google Maps Q82P+PC8, Dhapasi Marg, Tokha 44600, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>krishibhumi@outlook.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L15-6</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -811,7 +811,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -833,7 +833,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -877,7 +877,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -899,17 +899,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -919,25 +919,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>22</v>
+      <c r="F9" s="4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX27"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -997,7 +1019,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6473,10 +6495,8 @@
           <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9865036914</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9865036914</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6562,10 +6582,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -6576,29 +6594,29 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -6607,6 +6625,114 @@
       <c r="AX27" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:24 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -802,10 +802,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -956,10 +956,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1019,7 +1019,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6736,6 +6736,426 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:46 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359613</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9803269701</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803269701</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:13:23 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Bhadrakali English Medium School - General education school Q85W+7VJ Unnamed Road Budhanilkantha 446</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>grgashim20242@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>23:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>4d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:50:05 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:50:05 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>11d 18h 9m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>22</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1019,7 +1019,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6803,10 +6803,8 @@
           <t>lok bahadur malla</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9803269701</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9803269701</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6896,10 +6894,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6910,7 +6906,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -7011,10 +7007,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7104,47 +7098,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>11d 18h 9m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>11d 18h 9m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -7153,6 +7143,330 @@
       <c r="AX30" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:52 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
+      <c r="AA32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AC32" s="3" t="inlineStr"/>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1019,7 +1019,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7470,6 +7470,438 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363352</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9851026168</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9851026168</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:14:45 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>P7MP+QF3</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>near Your Choice Minimart , Nagarjun, Raniban Rd 1, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>mail.dawadi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>20:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB614</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365302</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9742917951</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9829489302</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:19:45 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.694486</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Near to Pathshala Foundation,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>kritikasah2331@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>03:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.332862</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -811,7 +811,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -833,17 +833,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -855,11 +855,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -899,17 +899,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -921,17 +921,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -941,25 +941,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>26</v>
+      <c r="F10" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -986,10 +1008,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -7537,10 +7559,8 @@
           <t>Rajan Dawadi</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9851026168</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9851026168</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7634,25 +7654,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB614</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7753,10 +7769,8 @@
           <t>Kritika Sah</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9742917951</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9742917951</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7850,55 +7864,259 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.332862</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33286200000001</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:40 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365176</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9851412379</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851412379</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:51:05 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Gai bachha chowk Gai bachha chowk - Hindu temple P72Q+Q59 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>9851412379@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>04:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>3h 46m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 48m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -1041,7 +1041,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7979,10 +7979,8 @@
           <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9851412379</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9851412379</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8072,10 +8070,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -8086,7 +8082,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>19</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -802,16 +802,16 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -833,17 +833,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -855,11 +855,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -877,7 +877,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
@@ -899,17 +899,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -921,17 +921,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -943,17 +943,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -963,25 +963,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>27</v>
+      <c r="E11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1029,19 +1051,19 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="35" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8116,6 +8138,846 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362110</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9866494523</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9869365032R</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:56 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Eresha cafe and restaurant - Family restaurant Kharibot Chowk Kharibot, , ,</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>Premkarki440@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>05:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364906</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9842868756</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>CHB9842868756</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:55:03 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>near by Sherpa Chowk - Shopping mall Sherpa Chowk Kapan 11 Budhanilkantha 44600, Kathmandu, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>9842868756@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>06:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L28-6</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 46m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365415</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9810289618</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>CHB9810289618</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:02 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>baudha ram hiti, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>sarmila74@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>3h 47m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365328</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shrestha</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shrestha</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9765565085</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9765565085</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:37:42 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.74183</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>CARPRO Basundhara Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>bishalshrestha98180073@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>04:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L3-8</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.32801</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -805,13 +805,13 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -833,7 +833,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -855,11 +855,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -877,11 +877,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
@@ -899,17 +899,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -921,17 +921,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router placement CR</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -985,25 +985,69 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="4" t="n">
+      <c r="C13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>31</v>
+      <c r="F13" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8205,10 +8249,8 @@
           <t>Prem Bahadur Karki</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9866494523</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9866494523</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8298,10 +8340,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -8312,7 +8352,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8413,10 +8453,8 @@
           <t>Pasang sherpa</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9842868756</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9842868756</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8506,10 +8544,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -8520,7 +8556,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8621,10 +8657,8 @@
           <t>Sarmila Sangasarar</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9810289618</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9810289618</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8714,10 +8748,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8728,7 +8760,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8829,10 +8861,8 @@
           <t>Bishal Shrestha</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9765565085</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9765565085</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8926,55 +8956,903 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L3-8</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.32801</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.32801000000001</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9747744379</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>LTP9747744379</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.680963</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Star Hospital, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>15:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB423</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.301988</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>4h 27m</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9747744379</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>LTP9747744379</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.680963</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Star Hospital, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>15:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB423</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.301988</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359002</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Thakur</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj kumar jha</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9849680028</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:27:45 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849680028</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:04:47 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:34:04 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>.., , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>1@g.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router placement CR</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>07:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>CDB521</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>5d 5h 29m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:55:59 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:21:37 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>22h 25m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4d 20h 23m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -811,17 +811,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -855,7 +855,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -877,11 +877,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
@@ -899,7 +899,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -921,17 +921,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -965,17 +965,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router placement CR</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router placement CR</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1009,7 +1009,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1029,25 +1029,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>34</v>
+      <c r="F14" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1061,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX44"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1079,7 +1101,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -1089,7 +1111,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -9061,20 +9083,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Suresh Raut</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9747744379</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9747744379</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9168,25 +9184,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB423</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.301988</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30198799999999</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -9277,20 +9289,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Suresh Raut</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9747744379</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9747744379</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9384,25 +9390,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>CDB423</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.301988</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.30198799999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9503,10 +9505,8 @@
           <t>Pankaj kumar jha</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9849680028</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9849680028</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9596,10 +9596,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -9610,7 +9608,7 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9711,10 +9709,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9804,47 +9800,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>22h 25m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4d 20h 23m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>22h 25m</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>4d 20h 23m</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV44" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -9853,6 +9845,214 @@
       <c r="AX44" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365547</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:31:20 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>02:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2h 32m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -1129,7 +1129,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9915,10 +9915,8 @@
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -10008,10 +10006,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -10022,7 +10018,7 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1129,7 +1129,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10052,6 +10052,646 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:35 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365327</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>dipa baral ghimire</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>dipa baral ghimire</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9851325162</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851325162</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:35:40 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>6 Saraswatinagar Rd - Building Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>9851325162@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>06:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>5h 59m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>10:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>10:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -1129,7 +1129,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10119,10 +10119,8 @@
           <t>dipa baral ghimire</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9851325162</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9851325162</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10212,10 +10210,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -10226,7 +10222,7 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -10327,10 +10323,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10424,25 +10418,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -10543,10 +10533,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10640,25 +10628,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -811,11 +811,11 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -855,7 +855,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -877,11 +877,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
@@ -921,17 +921,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -943,17 +943,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -1009,14 +1009,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1051,25 +1051,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>37</v>
+      <c r="F15" s="4" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1129,7 +1151,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10676,6 +10698,226 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 5:13 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>No signal</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364939</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Navraj Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Navraj Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9769760515</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9851007028</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:29:44 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.715288</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Dallu Swoyambhu bhagwan,Swoyambhu Bhagwan Pau , Swayambhu Cir Rd, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>navraj.shrestha22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>07:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.293141</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>21h 43m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -1151,7 +1151,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10765,10 +10765,8 @@
           <t>Navraj Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9769760515</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9769760515</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10844,10 +10842,8 @@
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH49" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH49" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
@@ -10866,25 +10862,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.293141</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.29314100000001</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>37</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>6</v>
@@ -805,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1082,7 +1082,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9</v>
@@ -1091,7 +1091,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1119,7 +1119,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -1151,10 +1151,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -10910,6 +10910,222 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 6:38 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355718</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841258917</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 06:38:07 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>nilambasnet</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:34:53 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 06:38:07 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.67657</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Dhobighat, near by  Progress Boys Hostel, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>javanbansent71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>18:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.30774</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_10_Oct_2026.xlsx
@@ -1151,7 +1151,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10977,10 +10977,8 @@
           <t>Nilam Karki Basnet</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841258917</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841258917</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -11074,25 +11072,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.30774</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.30774</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
